--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="undergarment" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>100300_100700_101200_101400_102200_101700_102100_101800_102500</t>
-  </si>
-  <si>
-    <t>100100_100700_101200_101400_102200_101700_102100_101800_102500</t>
   </si>
   <si>
     <t>金礦大亨</t>
@@ -1190,7 +1187,7 @@
         <v>100002</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>123123</v>
@@ -1433,8 +1430,9 @@
         <v>100100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C2"/>
       <c r="D2" t="str">
         <f>IF(C2&gt;0,A2,"")</f>
         <v/>
@@ -1445,7 +1443,7 @@
         <v>100300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1460,7 +1458,7 @@
         <v>100700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1475,7 +1473,7 @@
         <v>101200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1490,7 +1488,7 @@
         <v>101400</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1505,8 +1503,9 @@
         <v>102400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C7"/>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1517,7 +1516,7 @@
         <v>102200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1532,7 +1531,7 @@
         <v>101700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1547,7 +1546,7 @@
         <v>102100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1562,7 +1561,7 @@
         <v>101800</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1577,7 +1576,7 @@
         <v>102500</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1592,7 +1591,7 @@
         <v>102300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -1604,7 +1603,7 @@
         <v>103400</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -1616,7 +1615,7 @@
         <v>103500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -1628,7 +1627,7 @@
         <v>103501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
@@ -1640,7 +1639,7 @@
         <v>102000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1652,7 +1651,7 @@
         <v>103600</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -1664,7 +1663,7 @@
         <v>200100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
@@ -1676,7 +1675,7 @@
         <v>200101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
@@ -1688,7 +1687,7 @@
         <v>200300</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
@@ -1700,7 +1699,7 @@
         <v>200400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
@@ -1712,7 +1711,7 @@
         <v>200500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
@@ -1724,7 +1723,7 @@
         <v>200600</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
@@ -1736,7 +1735,7 @@
         <v>200700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
@@ -1748,7 +1747,7 @@
         <v>200800</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
@@ -1760,7 +1759,7 @@
         <v>200900</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
@@ -1772,7 +1771,7 @@
         <v>300100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
@@ -1784,7 +1783,7 @@
         <v>300200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
@@ -2317,7 +2316,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B29 A161:B1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B2 A3 B3 A4 B4 A5 B5 A6 B6 A7 B7 A8 B8 A9 B9 A10 B10 A11 B11 A12 B12 A13 B13 A14 B14 A15 B15 A16 B16 A17 B17 A18 B18 A19 B19 A20 B20 A21 B21 A22 B22 A23 B23 A24 B24 A25 B25 A26 B26 A27 B27 A28 B28 A29 B29 A161:B1048576" errorStyle="warning">
       <formula1>COUNTIF($A:$B,A2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="undergarment" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -58,10 +58,10 @@
     <t>googleClientID</t>
   </si>
   <si>
-    <t>100300_100700_101200_101400_102200_101700_102100_101800_102500</t>
-  </si>
-  <si>
-    <t>100100_100700_101200_101400_102200_101700_102100_101800_102500</t>
+    <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
+  </si>
+  <si>
+    <t>83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com</t>
   </si>
   <si>
     <t>金礦大亨</t>
@@ -792,7 +792,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -815,6 +815,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1132,8 +1135,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="56.325" customWidth="1"/>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="114.408333333333" customWidth="1"/>
+    <col min="3" max="3" width="80.7333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1181,8 +1184,8 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>123123</v>
+      <c r="C5" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1190,10 +1193,10 @@
         <v>100002</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C6">
-        <v>123123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1203,8 +1206,8 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
-        <v>123123</v>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1214,8 +1217,8 @@
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8">
-        <v>123123</v>
+      <c r="C8" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1225,8 +1228,8 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>123123</v>
+      <c r="C9" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1236,8 +1239,8 @@
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10">
-        <v>123123</v>
+      <c r="C10" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1247,8 +1250,8 @@
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11">
-        <v>123123</v>
+      <c r="C11" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1258,8 +1261,8 @@
       <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C12">
-        <v>123123</v>
+      <c r="C12" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1269,8 +1272,8 @@
       <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13">
-        <v>123123</v>
+      <c r="C13" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1280,8 +1283,8 @@
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14">
-        <v>123123</v>
+      <c r="C14" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1291,8 +1294,8 @@
       <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C15">
-        <v>123123</v>
+      <c r="C15" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1302,8 +1305,8 @@
       <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16">
-        <v>123123</v>
+      <c r="C16" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1313,8 +1316,8 @@
       <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C17">
-        <v>123123</v>
+      <c r="C17" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1324,8 +1327,8 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18">
-        <v>123123</v>
+      <c r="C18" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1335,8 +1338,8 @@
       <c r="B19" t="s">
         <v>9</v>
       </c>
-      <c r="C19">
-        <v>123123</v>
+      <c r="C19" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1346,8 +1349,8 @@
       <c r="B20" t="s">
         <v>9</v>
       </c>
-      <c r="C20">
-        <v>123123</v>
+      <c r="C20" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1357,8 +1360,8 @@
       <c r="B21" t="s">
         <v>9</v>
       </c>
-      <c r="C21">
-        <v>123123</v>
+      <c r="C21" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1368,8 +1371,8 @@
       <c r="B22" t="s">
         <v>9</v>
       </c>
-      <c r="C22">
-        <v>123123</v>
+      <c r="C22" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1379,8 +1382,8 @@
       <c r="B23" t="s">
         <v>9</v>
       </c>
-      <c r="C23">
-        <v>123123</v>
+      <c r="C23" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1390,8 +1393,8 @@
       <c r="B24" t="s">
         <v>9</v>
       </c>
-      <c r="C24">
-        <v>123123</v>
+      <c r="C24" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1401,11 +1404,34 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25">
-        <v>123123</v>
+      <c r="C25" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C6" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C7" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C9" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C11" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C13" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C15" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C17" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C19" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C21" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C23" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C25" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C8" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C10" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C12" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C14" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C16" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C18" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C20" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C22" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+    <hyperlink ref="C24" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1425,7 +1451,7 @@
     <row r="1" spans="1:4">
       <c r="D1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,D2:D29)</f>
-        <v>100300_100700_101200_101400_102200_101700_102100_101800_102500</v>
+        <v>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -1435,9 +1461,12 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="str">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <f>IF(C2&gt;0,A2,"")</f>
-        <v/>
+        <v>100100</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -1451,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D29" si="0">IF(C3&gt;0,A3,"")</f>
+        <f>IF(C3&gt;0,A3,"")</f>
         <v>100300</v>
       </c>
     </row>
@@ -1466,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:D29" si="0">IF(C4&gt;0,A4,"")</f>
         <v>100700</v>
       </c>
     </row>
@@ -1507,9 +1536,12 @@
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="str">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="0"/>
-        <v/>
+        <v>102400</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
@@ -1594,9 +1626,12 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" t="str">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="0"/>
-        <v/>
+        <v>102300</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:4">
@@ -1606,9 +1641,12 @@
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="str">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103400</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
@@ -1618,9 +1656,12 @@
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D15" t="str">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103500</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -1630,9 +1671,12 @@
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D16" t="str">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103501</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -1666,9 +1710,12 @@
       <c r="B19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" t="str">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200100</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -1678,9 +1725,12 @@
       <c r="B20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D20" t="str">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200101</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -1690,9 +1740,12 @@
       <c r="B21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D21" t="str">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200300</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -1702,9 +1755,12 @@
       <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="str">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200400</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -1714,9 +1770,12 @@
       <c r="B23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D23" t="str">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200500</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -1726,9 +1785,12 @@
       <c r="B24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D24" t="str">
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200600</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -1738,9 +1800,12 @@
       <c r="B25" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D25" t="str">
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200700</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -1750,9 +1815,12 @@
       <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D26" t="str">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200800</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -1762,9 +1830,12 @@
       <c r="B27" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D27" t="str">
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200900</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -1774,9 +1845,12 @@
       <c r="B28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D28" t="str">
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300100</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -1786,9 +1860,12 @@
       <c r="B29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D29" t="str">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300200</v>
       </c>
     </row>
     <row r="30" spans="1:4">

--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="undergarment" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -58,10 +58,7 @@
     <t>googleClientID</t>
   </si>
   <si>
-    <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
-  </si>
-  <si>
-    <t>83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com</t>
+    <t>100300_100700_101200_101400_102200_101700_102100_101800_102500</t>
   </si>
   <si>
     <t>金礦大亨</t>
@@ -792,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -815,9 +812,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1135,8 +1129,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="114.408333333333" customWidth="1"/>
-    <col min="3" max="3" width="80.7333333333333" customWidth="1"/>
+    <col min="2" max="2" width="56.325" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1184,8 +1178,8 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>10</v>
+      <c r="C5">
+        <v>123123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1195,8 +1189,8 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>10</v>
+      <c r="C6">
+        <v>123123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1206,8 +1200,8 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>10</v>
+      <c r="C7">
+        <v>123123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1217,8 +1211,8 @@
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>10</v>
+      <c r="C8">
+        <v>123123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1228,8 +1222,8 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>10</v>
+      <c r="C9">
+        <v>123123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1239,8 +1233,8 @@
       <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>10</v>
+      <c r="C10">
+        <v>123123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1250,8 +1244,8 @@
       <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>10</v>
+      <c r="C11">
+        <v>123123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1261,8 +1255,8 @@
       <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>10</v>
+      <c r="C12">
+        <v>123123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1272,8 +1266,8 @@
       <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>10</v>
+      <c r="C13">
+        <v>123123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1283,8 +1277,8 @@
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>10</v>
+      <c r="C14">
+        <v>123123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1294,8 +1288,8 @@
       <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>10</v>
+      <c r="C15">
+        <v>123123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1305,8 +1299,8 @@
       <c r="B16" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>10</v>
+      <c r="C16">
+        <v>123123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1316,8 +1310,8 @@
       <c r="B17" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>10</v>
+      <c r="C17">
+        <v>123123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1327,8 +1321,8 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>10</v>
+      <c r="C18">
+        <v>123123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1338,8 +1332,8 @@
       <c r="B19" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>10</v>
+      <c r="C19">
+        <v>123123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1349,8 +1343,8 @@
       <c r="B20" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>10</v>
+      <c r="C20">
+        <v>123123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1360,8 +1354,8 @@
       <c r="B21" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>10</v>
+      <c r="C21">
+        <v>123123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1371,8 +1365,8 @@
       <c r="B22" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>10</v>
+      <c r="C22">
+        <v>123123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1382,8 +1376,8 @@
       <c r="B23" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>10</v>
+      <c r="C23">
+        <v>123123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1393,8 +1387,8 @@
       <c r="B24" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>10</v>
+      <c r="C24">
+        <v>123123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1404,34 +1398,11 @@
       <c r="B25" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>10</v>
+      <c r="C25">
+        <v>123123</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C6" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C7" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C9" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C11" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C13" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C15" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C17" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C19" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C21" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C23" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C25" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C8" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C10" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C12" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C14" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C16" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C18" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C20" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C22" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C24" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1451,7 +1422,7 @@
     <row r="1" spans="1:4">
       <c r="D1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,D2:D29)</f>
-        <v>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</v>
+        <v>100300_100700_101200_101400_102200_101700_102100_101800_102500</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -1459,14 +1430,12 @@
         <v>100100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="str">
         <f>IF(C2&gt;0,A2,"")</f>
-        <v>100100</v>
+        <v/>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -1474,13 +1443,13 @@
         <v>100300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <f>IF(C3&gt;0,A3,"")</f>
+        <f t="shared" ref="D3:D29" si="0">IF(C3&gt;0,A3,"")</f>
         <v>100300</v>
       </c>
     </row>
@@ -1489,13 +1458,13 @@
         <v>100700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D3:D29" si="0">IF(C4&gt;0,A4,"")</f>
+        <f t="shared" si="0"/>
         <v>100700</v>
       </c>
     </row>
@@ -1504,7 +1473,7 @@
         <v>101200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1519,7 +1488,7 @@
         <v>101400</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1534,14 +1503,12 @@
         <v>102400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>102400</v>
+        <v>15</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
@@ -1549,7 +1516,7 @@
         <v>102200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1564,7 +1531,7 @@
         <v>101700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1579,7 +1546,7 @@
         <v>102100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1594,7 +1561,7 @@
         <v>101800</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1609,7 +1576,7 @@
         <v>102500</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1624,14 +1591,11 @@
         <v>102300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>102300</v>
+        <v>21</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:4">
@@ -1639,14 +1603,11 @@
         <v>103400</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>103400</v>
+        <v>22</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
@@ -1654,14 +1615,11 @@
         <v>103500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>103500</v>
+        <v>23</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -1669,14 +1627,11 @@
         <v>103501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>103501</v>
+        <v>24</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -1684,7 +1639,7 @@
         <v>102000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1696,7 +1651,7 @@
         <v>103600</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -1708,14 +1663,11 @@
         <v>200100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>200100</v>
+        <v>27</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -1723,14 +1675,11 @@
         <v>200101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>200101</v>
+        <v>28</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -1738,14 +1687,11 @@
         <v>200300</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>200300</v>
+        <v>29</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -1753,14 +1699,11 @@
         <v>200400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>200400</v>
+        <v>30</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -1768,14 +1711,11 @@
         <v>200500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>200500</v>
+        <v>31</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -1783,14 +1723,11 @@
         <v>200600</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>200600</v>
+        <v>32</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -1798,14 +1735,11 @@
         <v>200700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>200700</v>
+        <v>33</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -1813,14 +1747,11 @@
         <v>200800</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>200800</v>
+        <v>34</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -1828,14 +1759,11 @@
         <v>200900</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="0"/>
-        <v>200900</v>
+        <v>35</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -1843,14 +1771,11 @@
         <v>300100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="0"/>
-        <v>300100</v>
+        <v>36</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -1858,14 +1783,11 @@
         <v>300200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="0"/>
-        <v>300200</v>
+        <v>37</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2394,7 +2316,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B29 A161:B1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B2 A3 B3 A4 B4 A5 B5 A6 B6 A7 B7 A8 B8 A9 B9 A10 B10 A11 B11 A12 B12 A13 B13 A14 B14 A15 B15 A16 B16 A17 B17 A18 B18 A19 B19 A20 B20 A21 B21 A22 B22 A23 B23 A24 B24 A25 B25 A26 B26 A27 B27 A28 B28 A29 B29 A161:B1048576" errorStyle="warning">
       <formula1>COUNTIF($A:$B,A2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="undergarment" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -40,6 +40,12 @@
     <t>google信息</t>
   </si>
   <si>
+    <t>facebook信息</t>
+  </si>
+  <si>
+    <t>apple信息</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -56,6 +62,18 @@
   </si>
   <si>
     <t>googleClientID</t>
+  </si>
+  <si>
+    <t>facebookAppid</t>
+  </si>
+  <si>
+    <t>faceBookAppSecret</t>
+  </si>
+  <si>
+    <t>appleAppid</t>
+  </si>
+  <si>
+    <t>appleBundleId</t>
   </si>
   <si>
     <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
@@ -1131,15 +1149,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="114.408333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.375" customWidth="1"/>
     <col min="3" max="3" width="80.7333333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1149,164 +1171,200 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:7">
       <c r="A2" s="6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" ht="15" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:7">
       <c r="A3" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
       <c r="A4" s="7"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>100001</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>100002</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>100003</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>100004</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>100005</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>100006</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>100007</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>100008</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>100009</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>100010</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>100011</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>100012</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1314,10 +1372,10 @@
         <v>100013</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1325,10 +1383,10 @@
         <v>100014</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1336,10 +1394,10 @@
         <v>100015</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1347,10 +1405,10 @@
         <v>100016</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1358,10 +1416,10 @@
         <v>100017</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1369,10 +1427,10 @@
         <v>100018</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1380,10 +1438,10 @@
         <v>100019</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1391,10 +1449,10 @@
         <v>100020</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1402,10 +1460,10 @@
         <v>100021</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1459,7 +1517,7 @@
         <v>100100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1474,7 +1532,7 @@
         <v>100300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1489,7 +1547,7 @@
         <v>100700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1504,7 +1562,7 @@
         <v>101200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1519,7 +1577,7 @@
         <v>101400</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1534,7 +1592,7 @@
         <v>102400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1549,7 +1607,7 @@
         <v>102200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1564,7 +1622,7 @@
         <v>101700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1579,7 +1637,7 @@
         <v>102100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1594,7 +1652,7 @@
         <v>101800</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1609,7 +1667,7 @@
         <v>102500</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1624,7 +1682,7 @@
         <v>102300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1639,7 +1697,7 @@
         <v>103400</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1654,7 +1712,7 @@
         <v>103500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1669,7 +1727,7 @@
         <v>103501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1684,7 +1742,7 @@
         <v>102000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1696,7 +1754,7 @@
         <v>103600</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
@@ -1708,7 +1766,7 @@
         <v>200100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1723,7 +1781,7 @@
         <v>200101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1738,7 +1796,7 @@
         <v>200300</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1753,7 +1811,7 @@
         <v>200400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1768,7 +1826,7 @@
         <v>200500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1783,7 +1841,7 @@
         <v>200600</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1798,7 +1856,7 @@
         <v>200700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1813,7 +1871,7 @@
         <v>200800</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1828,7 +1886,7 @@
         <v>200900</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1843,7 +1901,7 @@
         <v>300100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1858,7 +1916,7 @@
         <v>300200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>1</v>

--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="48">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -76,10 +76,19 @@
     <t>appleBundleId</t>
   </si>
   <si>
-    <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
-  </si>
-  <si>
-    <t>83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com</t>
+    <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_103600_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
+  </si>
+  <si>
+    <t>1096197006732-ppv38doomu6n2h0ecd5jqgcoi8fqi64v.apps.googleusercontent.com</t>
+  </si>
+  <si>
+    <t>1053966183571466</t>
+  </si>
+  <si>
+    <t>be2794d79e8ffa4ac2bd070facd06091</t>
+  </si>
+  <si>
+    <t>com.jjg.777Slots</t>
   </si>
   <si>
     <t>金礦大亨</t>
@@ -810,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -829,13 +838,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1153,12 +1174,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="18.375" customWidth="1"/>
-    <col min="3" max="3" width="80.7333333333333" customWidth="1"/>
-    <col min="4" max="4" width="14.875" customWidth="1"/>
-    <col min="5" max="5" width="19.375" customWidth="1"/>
-    <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="2" max="2" width="171.758333333333" customWidth="1"/>
+    <col min="3" max="3" width="81.5" customWidth="1"/>
+    <col min="4" max="4" width="18.0333333333333" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="15.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="19.1" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1180,41 +1201,41 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -1226,14 +1247,14 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:7">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
@@ -1242,8 +1263,20 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" t="s">
         <v>16</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1253,8 +1286,20 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" t="s">
         <v>16</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1264,8 +1309,20 @@
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" t="s">
         <v>16</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1275,8 +1332,20 @@
       <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" t="s">
         <v>16</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1286,8 +1355,20 @@
       <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" t="s">
         <v>16</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1297,8 +1378,20 @@
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" t="s">
         <v>16</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1308,8 +1401,20 @@
       <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" t="s">
         <v>16</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1319,8 +1424,20 @@
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" t="s">
         <v>16</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1330,8 +1447,20 @@
       <c r="B13" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" t="s">
         <v>16</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1341,8 +1470,20 @@
       <c r="B14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" t="s">
         <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1352,8 +1493,20 @@
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" t="s">
         <v>16</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1363,133 +1516,230 @@
       <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>100013</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>100014</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>100015</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>100016</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>100017</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>100018</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>100019</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>100020</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>100021</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" t="s">
         <v>16</v>
       </c>
+      <c r="D25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C6" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C7" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C9" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C11" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C13" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C15" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C17" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C19" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C21" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C23" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C25" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C8" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C10" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C12" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C14" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C16" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C18" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C20" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C22" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-    <hyperlink ref="C24" r:id="rId1" display="83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com" tooltip="http://83752784171-e7jhpvh8nfca5q7n3po35r7ni6mq332n.apps.googleusercontent.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1503,13 +1753,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1"/>
-    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="D1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,D2:D29)</f>
-        <v>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</v>
+        <v>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_103600_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -1517,7 +1767,7 @@
         <v>100100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1532,13 +1782,13 @@
         <v>100300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <f>IF(C3&gt;0,A3,"")</f>
+        <f t="shared" ref="D3:D29" si="0">IF(C3&gt;0,A3,"")</f>
         <v>100300</v>
       </c>
     </row>
@@ -1547,13 +1797,13 @@
         <v>100700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D3:D29" si="0">IF(C4&gt;0,A4,"")</f>
+        <f t="shared" si="0"/>
         <v>100700</v>
       </c>
     </row>
@@ -1562,7 +1812,7 @@
         <v>101200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1577,7 +1827,7 @@
         <v>101400</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1592,7 +1842,7 @@
         <v>102400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1607,7 +1857,7 @@
         <v>102200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1622,7 +1872,7 @@
         <v>101700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1637,7 +1887,7 @@
         <v>102100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1652,7 +1902,7 @@
         <v>101800</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1667,7 +1917,7 @@
         <v>102500</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1682,7 +1932,7 @@
         <v>102300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1697,7 +1947,7 @@
         <v>103400</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1712,7 +1962,7 @@
         <v>103500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1727,7 +1977,7 @@
         <v>103501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1742,7 +1992,7 @@
         <v>102000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1754,11 +2004,14 @@
         <v>103600</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="str">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103600</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -1766,7 +2019,7 @@
         <v>200100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1781,7 +2034,7 @@
         <v>200101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1796,7 +2049,7 @@
         <v>200300</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1811,7 +2064,7 @@
         <v>200400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1826,7 +2079,7 @@
         <v>200500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1841,7 +2094,7 @@
         <v>200600</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1856,7 +2109,7 @@
         <v>200700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1871,7 +2124,7 @@
         <v>200800</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1886,7 +2139,7 @@
         <v>200900</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1901,7 +2154,7 @@
         <v>300100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1916,7 +2169,7 @@
         <v>300200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>1</v>

--- a/account/resources/sample/undergarment.xlsx
+++ b/account/resources/sample/undergarment.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="48">
   <si>
     <t>马甲包名称</t>
   </si>
@@ -40,6 +40,12 @@
     <t>google信息</t>
   </si>
   <si>
+    <t>facebook信息</t>
+  </si>
+  <si>
+    <t>apple信息</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -58,7 +64,31 @@
     <t>googleClientID</t>
   </si>
   <si>
-    <t>100300_100700_101200_101400_102200_101700_102100_101800_102500</t>
+    <t>facebookAppid</t>
+  </si>
+  <si>
+    <t>faceBookAppSecret</t>
+  </si>
+  <si>
+    <t>appleAppid</t>
+  </si>
+  <si>
+    <t>appleBundleId</t>
+  </si>
+  <si>
+    <t>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_103600_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</t>
+  </si>
+  <si>
+    <t>1096197006732-ppv38doomu6n2h0ecd5jqgcoi8fqi64v.apps.googleusercontent.com</t>
+  </si>
+  <si>
+    <t>1053966183571466</t>
+  </si>
+  <si>
+    <t>be2794d79e8ffa4ac2bd070facd06091</t>
+  </si>
+  <si>
+    <t>com.jjg.777Slots</t>
   </si>
   <si>
     <t>金礦大亨</t>
@@ -789,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -808,10 +838,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1125,15 +1170,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="56.325" customWidth="1"/>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="171.758333333333" customWidth="1"/>
+    <col min="3" max="3" width="81.5" customWidth="1"/>
+    <col min="4" max="4" width="18.0333333333333" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="15.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="19.1" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1143,263 +1192,551 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:7">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" ht="15" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:7">
+      <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>100001</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>100002</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>100003</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>100004</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>100005</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>100006</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>100007</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>100008</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>100009</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>100010</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>100011</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>100012</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>100013</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>100014</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>100015</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>100016</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>100017</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>100018</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>100019</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>100020</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>100021</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25">
-        <v>123123</v>
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="10">
+        <v>6758744755</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1416,13 +1753,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1"/>
-    <col min="2" max="2" width="10.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="D1" t="str">
         <f>_xlfn.TEXTJOIN("_",TRUE,D2:D29)</f>
-        <v>100300_100700_101200_101400_102200_101700_102100_101800_102500</v>
+        <v>100100_100300_100700_101200_101400_102400_102200_101700_102100_101800_102500_102300_103400_103500_103501_103600_200100_200101_200300_200400_200500_200600_200700_200800_200900_300100_300200</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -1430,12 +1767,14 @@
         <v>100100</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2" t="str">
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
         <f>IF(C2&gt;0,A2,"")</f>
-        <v/>
+        <v>100100</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -1443,7 +1782,7 @@
         <v>100300</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1458,7 +1797,7 @@
         <v>100700</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1473,7 +1812,7 @@
         <v>101200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1488,7 +1827,7 @@
         <v>101400</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1503,12 +1842,14 @@
         <v>102400</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7" t="str">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="0"/>
-        <v/>
+        <v>102400</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
@@ -1516,7 +1857,7 @@
         <v>102200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1531,7 +1872,7 @@
         <v>101700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1546,7 +1887,7 @@
         <v>102100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1561,7 +1902,7 @@
         <v>101800</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1576,7 +1917,7 @@
         <v>102500</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1591,11 +1932,14 @@
         <v>102300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="str">
+        <v>31</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="0"/>
-        <v/>
+        <v>102300</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:4">
@@ -1603,11 +1947,14 @@
         <v>103400</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="str">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103400</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
@@ -1615,11 +1962,14 @@
         <v>103500</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="str">
+        <v>33</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103500</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
@@ -1627,11 +1977,14 @@
         <v>103501</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="str">
+        <v>34</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103501</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -1639,7 +1992,7 @@
         <v>102000</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
@@ -1651,11 +2004,14 @@
         <v>103600</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" t="str">
+        <v>36</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
         <f t="shared" si="0"/>
-        <v/>
+        <v>103600</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -1663,11 +2019,14 @@
         <v>200100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="str">
+        <v>37</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200100</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -1675,11 +2034,14 @@
         <v>200101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="str">
+        <v>38</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200101</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -1687,11 +2049,14 @@
         <v>200300</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="str">
+        <v>39</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200300</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -1699,11 +2064,14 @@
         <v>200400</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="str">
+        <v>40</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200400</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
@@ -1711,11 +2079,14 @@
         <v>200500</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" t="str">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200500</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
@@ -1723,11 +2094,14 @@
         <v>200600</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="str">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200600</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
@@ -1735,11 +2109,14 @@
         <v>200700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" t="str">
+        <v>43</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200700</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
@@ -1747,11 +2124,14 @@
         <v>200800</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" t="str">
+        <v>44</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200800</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
@@ -1759,11 +2139,14 @@
         <v>200900</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" t="str">
+        <v>45</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
         <f t="shared" si="0"/>
-        <v/>
+        <v>200900</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
@@ -1771,11 +2154,14 @@
         <v>300100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="str">
+        <v>46</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300100</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:4">
@@ -1783,11 +2169,14 @@
         <v>300200</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="str">
+        <v>47</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
         <f t="shared" si="0"/>
-        <v/>
+        <v>300200</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2316,7 +2705,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B2 A3 B3 A4 B4 A5 B5 A6 B6 A7 B7 A8 B8 A9 B9 A10 B10 A11 B11 A12 B12 A13 B13 A14 B14 A15 B15 A16 B16 A17 B17 A18 B18 A19 B19 A20 B20 A21 B21 A22 B22 A23 B23 A24 B24 A25 B25 A26 B26 A27 B27 A28 B28 A29 B29 A161:B1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="A2:B29 A161:B1048576" errorStyle="warning">
       <formula1>COUNTIF($A:$B,A2)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
